--- a/20250519_ErCoIn_SA/output/20250519_ErCoIn_SA_site_pairs.xlsx
+++ b/20250519_ErCoIn_SA/output/20250519_ErCoIn_SA_site_pairs.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,11 +452,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1818414.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.623</v>
+        <v>2.231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -467,56 +467,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1818414.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.662</v>
+        <v>2.363</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deficiency without atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1234749.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.727</v>
+        <v>2.46</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Deficiency without atomic mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1234749.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.742</v>
+        <v>2.482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deficiency without atomic mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1956508.cif</t>
+          <t>1925389.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.799</v>
+        <v>2.492</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -531,11 +531,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.055</v>
+        <v>2.964</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.768</v>
+        <v>2.499</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.154</v>
+        <v>0.248</v>
       </c>
       <c r="C10" t="inlineStr"/>
     </row>
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,59 +600,359 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1956508.cif</t>
+          <t>1234749.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.687</v>
+        <v>2.859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deficiency without atomic mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1234749.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.964</v>
+        <v>2.869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deficiency with atomic mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1634753.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.959</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>1818414.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.826</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>2.962</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>1140826.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1234747.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.035</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.051</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1229705.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.137</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1840445.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.174</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1710931.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.199</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1840445.cif</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.201</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1229705.cif</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.205</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.207</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1920543.cif</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3.222</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.239</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1818414.cif</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.314</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1234747.cif</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.346</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1140826.cif</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3.359</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3.143</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -665,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,11 +988,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1956508.cif</t>
+          <t>1814810.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.949</v>
+        <v>2.623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -703,11 +1003,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1803318.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.009</v>
+        <v>2.644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -722,40 +1022,550 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2</v>
+        <v>2.662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1840445.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.691</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>1814810.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.053</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>2.727</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1818414.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1234747.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.737</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1140826.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.743</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1818414.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.758</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.774</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1229705.cif</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.794</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1140826.cif</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.797</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1956508.cif</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1000761.cif</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1234747.cif</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.821</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1234747.cif</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1840445.cif</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1234749.cif</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1229705.cif</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.863</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1234749.cif</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.869</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1229705.cif</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2.872</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1233938.cif</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1818414.cif</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2.888</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1140826.cif</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2.918</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1925389.cif</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.922</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1840445.cif</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.925</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1818414.cif</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2.962</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1233938.cif</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.976</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1233938.cif</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.983</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2.985</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3.009</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1233938.cif</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3.009</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -768,7 +1578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,26 +1601,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1634753.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.055</v>
+        <v>2.447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1234749.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,44 +1631,389 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1234749.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.294</v>
+        <v>2.482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.618</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>1233938.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.183</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>2.626</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.674</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1233938.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.676</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1233938.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.677</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.678</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1956508.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1920543.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1710931.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.691</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.693</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1233938.cif</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.698</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1000761.cif</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.705</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1233938.cif</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1233938.cif</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1803512.cif</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1840445.cif</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.813</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1925389.cif</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.922</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1229705.cif</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1229705.cif</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3.071</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1840445.cif</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.122</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.738</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -871,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,42 +2049,209 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1814810.cif</t>
+          <t>1234749.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.964</v>
+        <v>2.46</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deficiency with atomic mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1234749.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>1229705.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2.926</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1000761.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.948</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1956508.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.949</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1840445.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.967</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.009</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1920543.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1710931.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.199</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1814810.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1920543.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.224</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.954</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
